--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92554605559</v>
+        <v>46157.93110676298</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93110676298</v>
+        <v>46157.93134701299</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93134701299</v>
+        <v>46157.93382363633</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93382363633</v>
+        <v>46157.93694116644</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93694116644</v>
+        <v>46158.28204256942</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28204256942</v>
+        <v>46158.29651216405</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29651216405</v>
+        <v>46158.29806018878</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29806018878</v>
+        <v>46158.33369130398</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33369130398</v>
+        <v>46158.37220846249</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/11_Поставщики/21. Статус-2 (Мира, 59)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37220846249</v>
+        <v>46158.37274823899</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
